--- a/output/paket/03_ELEKTRİK/Gym_Elektrik_BoQ.xlsx
+++ b/output/paket/03_ELEKTRİK/Gym_Elektrik_BoQ.xlsx
@@ -712,7 +712,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rev G · 17 Eylül 2026 · Eylül 2026 · Aqua Florya / Saltbae kesin hakedişi (Mayıs 2025) birim fiyatları ×1,40 eskalasyonla · Ekipman işverence temin edilmiştir, bütçe dışıdır.</t>
+          <t>Rev H · 17 Eylül 2026 · Eylül 2026 · Aqua Florya / Saltbae kesin hakedişi (Mayıs 2025) birim fiyatları ×1,40 eskalasyonla · Ekipman işverence temin edilmiştir, bütçe dışıdır.</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev G · 17 Eylül 2026 · Fiyat referansı: Eylül 2026 · Aqua Florya / Saltbae kesin hakedişi (Mayıs 2025) birim fiyatları ×1,40 eskalasyonla · Birim fiyat sütununu (F) doldurun, tutarlar kendiliğinden hesaplanır</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev H · 17 Eylül 2026 · Fiyat referansı: Eylül 2026 · Aqua Florya / Saltbae kesin hakedişi (Mayıs 2025) birim fiyatları ×1,40 eskalasyonla · Birim fiyat sütununu (F) doldurun, tutarlar kendiliğinden hesaplanır</t>
         </is>
       </c>
     </row>

--- a/output/paket/03_ELEKTRİK/Gym_Elektrik_BoQ.xlsx
+++ b/output/paket/03_ELEKTRİK/Gym_Elektrik_BoQ.xlsx
@@ -2156,7 +2156,7 @@
         </is>
       </c>
       <c r="E35" s="29" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F35" s="22" t="n"/>
       <c r="G35" s="30">
@@ -2164,10 +2164,10 @@
         <v/>
       </c>
       <c r="H35" s="31" t="n">
-        <v>12600</v>
+        <v>12720</v>
       </c>
       <c r="I35" s="31" t="n">
-        <v>22050</v>
+        <v>22260</v>
       </c>
     </row>
     <row r="36">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="B31" s="35" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
